--- a/seed/naidis-partnerid.xlsx
+++ b/seed/naidis-partnerid.xlsx
@@ -31,7 +31,7 @@
     <t>e_post</t>
   </si>
   <si>
-    <t>uhikhind</t>
+    <t>uhikuhind</t>
   </si>
   <si>
     <t>Tehisaru Koolitus OÜ</t>
@@ -52,7 +52,7 @@
     <t>jaan.kask@tehisaru-naidis.ee</t>
   </si>
   <si>
-    <t>1450</t>
+    <t>58</t>
   </si>
   <si>
     <t>AI Akadeemia OÜ</t>
@@ -70,7 +70,7 @@
     <t>liis.magi@ai-akadeemia-naidis.ee</t>
   </si>
   <si>
-    <t>1515</t>
+    <t>60,50</t>
   </si>
   <si>
     <t>Nutikoolitus OÜ</t>
@@ -88,7 +88,7 @@
     <t>kadri.lepik@nutikoolitus-naidis.ee</t>
   </si>
   <si>
-    <t>1580</t>
+    <t>63</t>
   </si>
   <si>
     <t>Targa Töö Koolitus OÜ</t>
@@ -106,7 +106,7 @@
     <t>anu.sepp@targatoo-naidis.ee</t>
   </si>
   <si>
-    <t>1645</t>
+    <t>65,50</t>
   </si>
   <si>
     <t>E-õppe Ekspert OÜ</t>
@@ -124,13 +124,13 @@
     <t>toomas.rand@eoppe-naidis.ee</t>
   </si>
   <si>
-    <t>1710</t>
+    <t>68</t>
   </si>
   <si>
     <t>OSA-2</t>
   </si>
   <si>
-    <t>980</t>
+    <t>39</t>
   </si>
   <si>
     <t>Digioskus MTÜ</t>
@@ -145,43 +145,43 @@
     <t>peeter.saar@digioskus-naidis.ee</t>
   </si>
   <si>
-    <t>1040</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>1160</t>
+    <t>41,50</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>46,50</t>
   </si>
   <si>
     <t>OSA-3</t>
   </si>
   <si>
-    <t>760</t>
-  </si>
-  <si>
-    <t>820</t>
-  </si>
-  <si>
-    <t>880</t>
-  </si>
-  <si>
-    <t>940</t>
-  </si>
-  <si>
-    <t>1000</t>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17,50</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20,50</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>OSA-4</t>
   </si>
   <si>
-    <t>4800</t>
-  </si>
-  <si>
-    <t>5300</t>
-  </si>
-  <si>
-    <t>5800</t>
+    <t>27</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>33</t>
   </si>
 </sst>
 </file>
@@ -570,7 +570,7 @@
     <col min="3" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
